--- a/Customized Program Main Dataframe Structure.xlsx
+++ b/Customized Program Main Dataframe Structure.xlsx
@@ -1,36 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12EBC87F-5074-4463-8423-B56DAF23AB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7FA90F-E48F-4AD2-8D90-3D732B341B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="6" xr2:uid="{B2D932DB-2183-440F-AF66-43F3E8354BB0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{B2D932DB-2183-440F-AF66-43F3E8354BB0}"/>
   </bookViews>
   <sheets>
     <sheet name="05 - mastery_header" sheetId="3" r:id="rId1"/>
     <sheet name="05 - ranked_header" sheetId="4" r:id="rId2"/>
     <sheet name="05 - LoLGame_info_header" sheetId="6" r:id="rId3"/>
     <sheet name="05 - LoLGame_timeline_header" sheetId="5" r:id="rId4"/>
-    <sheet name="05 - TFTHistory_header" sheetId="7" r:id="rId5"/>
-    <sheet name="05 - TFTGame_info_header" sheetId="9" r:id="rId6"/>
-    <sheet name="07 - catalog_header" sheetId="12" r:id="rId7"/>
-    <sheet name="07 - collection_header" sheetId="13" r:id="rId8"/>
-    <sheet name="09 - queues_header" sheetId="2" r:id="rId9"/>
-    <sheet name="11 - LoLGame_info_header" sheetId="1" r:id="rId10"/>
-    <sheet name="11 - TFTHistory_header" sheetId="10" r:id="rId11"/>
-    <sheet name="12 - player_loot_header" sheetId="11" r:id="rId12"/>
+    <sheet name="05 - LoLGame_event_header" sheetId="14" r:id="rId5"/>
+    <sheet name="05 - TFTHistory_header" sheetId="7" r:id="rId6"/>
+    <sheet name="05 - TFTGame_info_header" sheetId="9" r:id="rId7"/>
+    <sheet name="07 - catalog_header" sheetId="12" r:id="rId8"/>
+    <sheet name="07 - collection_header" sheetId="13" r:id="rId9"/>
+    <sheet name="09 - queues_header" sheetId="2" r:id="rId10"/>
+    <sheet name="11 - LoLGame_info_header" sheetId="1" r:id="rId11"/>
+    <sheet name="11 - TFTHistory_header" sheetId="10" r:id="rId12"/>
+    <sheet name="12 - player_loot_header" sheetId="11" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'05 - LoLGame_info_header'!$A$1:$E$142</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'05 - TFTHistory_header'!$A$1:$E$160</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'11 - LoLGame_info_header'!$A$1:$E$149</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'11 - TFTHistory_header'!$A$1:$E$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05 - TFTHistory_header'!$A$1:$E$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'11 - LoLGame_info_header'!$A$1:$E$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11 - TFTHistory_header'!$A$1:$E$160</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -53,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="940">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="997">
   <si>
     <t>gameCreationDate</t>
   </si>
@@ -3037,13 +3038,201 @@
   <si>
     <t>价格（点券）</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assistingParticipantIds</t>
+  </si>
+  <si>
+    <t>buildingType</t>
+  </si>
+  <si>
+    <t>被摧毁的建筑物类型</t>
+  </si>
+  <si>
+    <t>killerId</t>
+  </si>
+  <si>
+    <t>laneType</t>
+  </si>
+  <si>
+    <t>线路位置</t>
+  </si>
+  <si>
+    <t>monsterSubType</t>
+  </si>
+  <si>
+    <t>野区生物亚型</t>
+  </si>
+  <si>
+    <t>monsterType</t>
+  </si>
+  <si>
+    <t>野区生物类型</t>
+  </si>
+  <si>
+    <t>位置坐标</t>
+  </si>
+  <si>
+    <t>skillSlot</t>
+  </si>
+  <si>
+    <t>学习技能槽位</t>
+  </si>
+  <si>
+    <t>teamId</t>
+  </si>
+  <si>
+    <t>towerType</t>
+  </si>
+  <si>
+    <t>防御塔类型</t>
+  </si>
+  <si>
+    <t>事件类型</t>
+  </si>
+  <si>
+    <t>victimId</t>
+  </si>
+  <si>
+    <t>assistingChampion</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assistingChampionAlias</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assistingParticipantGameName#TagLine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>item</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得的装备序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>获得的装备</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>killerChampion</t>
+  </si>
+  <si>
+    <t>killerChampionAlias</t>
+  </si>
+  <si>
+    <t>killerParticipantGameName#TagLine</t>
+  </si>
+  <si>
+    <t>事件参与者序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>champion</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>championAlias</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>participantGameName#TagLine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>victimChampion</t>
+  </si>
+  <si>
+    <t>victimChampionAlias</t>
+  </si>
+  <si>
+    <t>victimParticipantGameName#TagLine</t>
+  </si>
+  <si>
+    <t>助攻者序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀者序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>被杀者序号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>助攻者英雄</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>助攻者英雄名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>assistingParticipantSummonerName</t>
+  </si>
+  <si>
+    <t>killerParticipantSummonerName</t>
+  </si>
+  <si>
+    <t>participantSummonerName</t>
+  </si>
+  <si>
+    <t>victimParticipantSummonerName</t>
+  </si>
+  <si>
+    <t>助攻者召唤师名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>助攻者游戏名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>击杀者英雄</t>
+  </si>
+  <si>
+    <t>击杀者英雄名称</t>
+  </si>
+  <si>
+    <t>击杀者召唤师名</t>
+  </si>
+  <si>
+    <t>击杀者游戏名</t>
+  </si>
+  <si>
+    <t>参与者英雄</t>
+  </si>
+  <si>
+    <t>参与者英雄名称</t>
+  </si>
+  <si>
+    <t>参与者召唤师名</t>
+  </si>
+  <si>
+    <t>参与者游戏名</t>
+  </si>
+  <si>
+    <t>被杀者英雄</t>
+  </si>
+  <si>
+    <t>被杀者英雄名称</t>
+  </si>
+  <si>
+    <t>被杀者召唤师名</t>
+  </si>
+  <si>
+    <t>被杀者游戏名</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3068,6 +3257,11 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -3166,7 +3360,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3264,6 +3458,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3837,6 +4043,935 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8672D3B3-4AAA-4AC1-99DA-D800CB3EF628}">
+  <dimension ref="A1:E56"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="13">
+        <v>0</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="13">
+        <v>1</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="13">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="13">
+        <v>3</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="13">
+        <v>4</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>832</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>848</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="13">
+        <v>5</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>834</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>835</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="13">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="13">
+        <v>7</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="13">
+        <v>8</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="13">
+        <v>9</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>836</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>837</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="13">
+        <v>10</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>12</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="13">
+        <v>13</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
+        <v>14</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="13">
+        <v>15</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E17">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="13">
+        <v>16</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E18">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="13">
+        <v>17</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="13">
+        <v>18</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="13">
+        <v>19</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="13">
+        <v>20</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="13">
+        <v>21</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="13">
+        <v>22</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="13">
+        <v>23</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>838</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>839</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="13">
+        <v>24</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="13">
+        <v>25</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>233</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" t="s">
+        <v>195</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="13">
+        <v>27</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>194</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="13">
+        <v>28</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
+        <v>29</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E31">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
+        <v>30</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E32">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
+        <v>33</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
+        <v>34</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
+        <v>35</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="3">
+        <v>36</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E38">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="3">
+        <v>37</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E39">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="3">
+        <v>38</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="3">
+        <v>39</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="D41" s="7"/>
+    </row>
+    <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="3">
+        <v>40</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="3">
+        <v>41</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E43">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44" s="3">
+        <v>42</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E44">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="3">
+        <v>43</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E45">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="3">
+        <v>44</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E46">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="3">
+        <v>45</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="D47" s="7"/>
+    </row>
+    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="3">
+        <v>46</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E48">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="3">
+        <v>47</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="3">
+        <v>48</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51" s="3">
+        <v>49</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E51">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52" s="3">
+        <v>50</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E52">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53" s="15">
+        <v>51</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54" s="15">
+        <v>52</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E54">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55" s="15">
+        <v>53</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E55">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56" s="15">
+        <v>54</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>846</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>847</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>833</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E55">
+    <sortCondition ref="A1:A55"/>
+  </sortState>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E653D2-5962-4B6A-AE49-EF482E17CB95}">
   <dimension ref="A1:E149"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -6175,7 +7310,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53D464B7-2503-4E39-93C9-118A187675BB}">
   <dimension ref="A1:E160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -8460,7 +9595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89B45046-550B-4F7D-838A-D2B016D38862}">
   <dimension ref="A1:E35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -11866,6 +13001,506 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EABD42D6-1F8D-4C17-9D66-8626EB853085}">
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="40.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="33">
+        <v>0</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>940</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>974</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>958</v>
+      </c>
+      <c r="C3" t="s">
+        <v>977</v>
+      </c>
+      <c r="E3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>959</v>
+      </c>
+      <c r="C4" t="s">
+        <v>978</v>
+      </c>
+      <c r="E4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>979</v>
+      </c>
+      <c r="C5" t="s">
+        <v>983</v>
+      </c>
+      <c r="E5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>960</v>
+      </c>
+      <c r="C6" t="s">
+        <v>984</v>
+      </c>
+      <c r="E6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>941</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>942</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>860</v>
+      </c>
+      <c r="C8" s="33" t="s">
+        <v>962</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>961</v>
+      </c>
+      <c r="C9" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>943</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>975</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="35" t="s">
+        <v>964</v>
+      </c>
+      <c r="C11" t="s">
+        <v>985</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12" s="35" t="s">
+        <v>965</v>
+      </c>
+      <c r="C12" t="s">
+        <v>986</v>
+      </c>
+      <c r="E12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="35" t="s">
+        <v>980</v>
+      </c>
+      <c r="C13" t="s">
+        <v>987</v>
+      </c>
+      <c r="E13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>966</v>
+      </c>
+      <c r="C14" t="s">
+        <v>988</v>
+      </c>
+      <c r="E14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>944</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>945</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>946</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>947</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>948</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>949</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" s="33" t="s">
+        <v>967</v>
+      </c>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>968</v>
+      </c>
+      <c r="C19" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>969</v>
+      </c>
+      <c r="C20" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="35" t="s">
+        <v>981</v>
+      </c>
+      <c r="C21" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>970</v>
+      </c>
+      <c r="C22" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>950</v>
+      </c>
+      <c r="D23" s="7"/>
+      <c r="E23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>22</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>951</v>
+      </c>
+      <c r="C24" s="33" t="s">
+        <v>952</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>23</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>953</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>24</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>328</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>25</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>329</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>330</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>26</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>954</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>955</v>
+      </c>
+      <c r="D28" s="7"/>
+      <c r="E28">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>27</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>956</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>28</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>957</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>976</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>29</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>971</v>
+      </c>
+      <c r="C31" t="s">
+        <v>993</v>
+      </c>
+      <c r="E31">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>30</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>972</v>
+      </c>
+      <c r="C32" t="s">
+        <v>994</v>
+      </c>
+      <c r="E32">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>31</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>982</v>
+      </c>
+      <c r="C33" t="s">
+        <v>995</v>
+      </c>
+      <c r="E33">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34">
+        <v>32</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>973</v>
+      </c>
+      <c r="C34" t="s">
+        <v>996</v>
+      </c>
+      <c r="E34">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D11711-B3DD-4521-85ED-C5C33898C2FE}">
   <dimension ref="A1:E160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -14141,7 +15776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D567C431-8C59-4F86-AD97-9551E441806C}">
   <dimension ref="A1:E151"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -16294,7 +17929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9078C510-49E8-4816-91AD-BE458B8B69FF}">
   <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -16650,7 +18285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1825EA8B-04E8-4ED7-BEFA-85B1FF72FE52}">
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -16913,933 +18548,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8672D3B3-4AAA-4AC1-99DA-D800CB3EF628}">
-  <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D1" t="s">
-        <v>352</v>
-      </c>
-      <c r="E1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="13">
-        <v>0</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="13">
-        <v>1</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A4" s="13">
-        <v>2</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="13">
-        <v>3</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>225</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="13">
-        <v>4</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>832</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>848</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>833</v>
-      </c>
-      <c r="E6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="13">
-        <v>5</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>834</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>835</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="13">
-        <v>6</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="13">
-        <v>7</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="13">
-        <v>8</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="13">
-        <v>9</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>836</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>837</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="13">
-        <v>10</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="13">
-        <v>11</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>219</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="13">
-        <v>12</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E14">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="13">
-        <v>13</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E15">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="13">
-        <v>14</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="D16" s="7"/>
-      <c r="E16">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="13">
-        <v>15</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E17">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18" s="13">
-        <v>16</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E18">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="13">
-        <v>17</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20" s="13">
-        <v>18</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="13">
-        <v>19</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E21">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="13">
-        <v>20</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="13">
-        <v>21</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="D23" s="7"/>
-      <c r="E23">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="13">
-        <v>22</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E24">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25" s="13">
-        <v>23</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>838</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>839</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="13">
-        <v>24</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E26">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A27" s="13">
-        <v>25</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>26</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="C28" t="s">
-        <v>195</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="13">
-        <v>27</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="13">
-        <v>28</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="3">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E31">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32" s="3">
-        <v>30</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E32">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33" s="3">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D33" s="7"/>
-      <c r="E33">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="3">
-        <v>32</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E34">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="3">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E35">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="3">
-        <v>34</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E36">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37" s="3">
-        <v>35</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>840</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="3">
-        <v>36</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E38">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="3">
-        <v>37</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E39">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="3">
-        <v>38</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41" s="3">
-        <v>39</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>842</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>844</v>
-      </c>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="3">
-        <v>40</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A43" s="3">
-        <v>41</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E43">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A44" s="3">
-        <v>42</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E44">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A45" s="3">
-        <v>43</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E45">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A46" s="3">
-        <v>44</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E46">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A47" s="3">
-        <v>45</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>843</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>845</v>
-      </c>
-      <c r="D47" s="7"/>
-    </row>
-    <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A48" s="3">
-        <v>46</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E48">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A49" s="3">
-        <v>47</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D49" s="7"/>
-      <c r="E49">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A50" s="3">
-        <v>48</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E50">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A51" s="3">
-        <v>49</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E51">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A52" s="3">
-        <v>50</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E52">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A53" s="15">
-        <v>51</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E53">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A54" s="15">
-        <v>52</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E54">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A55" s="15">
-        <v>53</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E55">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A56" s="15">
-        <v>54</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>846</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>847</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>833</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E55">
-    <sortCondition ref="A1:A55"/>
-  </sortState>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Customized Program Main Dataframe Structure.xlsx
+++ b/Customized Program Main Dataframe Structure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7FA90F-E48F-4AD2-8D90-3D732B341B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0FC01E-97E2-4DA2-8AAB-BE87616C63C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="4" xr2:uid="{B2D932DB-2183-440F-AF66-43F3E8354BB0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B2D932DB-2183-440F-AF66-43F3E8354BB0}"/>
   </bookViews>
   <sheets>
     <sheet name="05 - mastery_header" sheetId="3" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="1008">
   <si>
     <t>gameCreationDate</t>
   </si>
@@ -3004,26 +3004,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>formattedChampionPoints</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>formattedMasteryGoal</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>总成就点数（千位分隔符）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>下一级成就点数（千位分隔符）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>playerId</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>price_IP</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -3226,6 +3206,60 @@
   </si>
   <si>
     <t>被杀者游戏名</t>
+  </si>
+  <si>
+    <t>当前赛季英雄成就里程点</t>
+  </si>
+  <si>
+    <t>markRequiredForNextLevel</t>
+  </si>
+  <si>
+    <t>milestoneGrades</t>
+  </si>
+  <si>
+    <t>已取得的对局评价</t>
+  </si>
+  <si>
+    <t>nextSeasonMilestoneBonus</t>
+  </si>
+  <si>
+    <t>已达到IV级里程碑</t>
+  </si>
+  <si>
+    <t>nextSeasonMilestoneMaximumReward</t>
+  </si>
+  <si>
+    <t>下个里程点最大奖励次数</t>
+  </si>
+  <si>
+    <t>nextSeasonMilestoneRewardValue</t>
+  </si>
+  <si>
+    <t>下个里程点奖励物品序号</t>
+  </si>
+  <si>
+    <t>nextSeasonMilestoneRewardMarks</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下个里程点奖励英雄成就标记个数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>championSeasonMilestone</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>nextSeasonMilestoneRequireGrade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下个里程点所需对局评价</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下一级成就所需英雄成就标记个数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3360,7 +3394,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3460,16 +3494,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3798,11 +3826,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AF82C05-E00D-47FE-907F-7796571974D3}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="31.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.75" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3926,16 +3954,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>248</v>
+        <v>1004</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>249</v>
+        <v>992</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3943,40 +3971,48 @@
         <v>7</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>931</v>
+        <v>248</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>933</v>
-      </c>
-      <c r="D9" s="7"/>
+        <v>249</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E9">
+        <v>8</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="15">
         <v>8</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>932</v>
+        <v>250</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>934</v>
-      </c>
-      <c r="D10" s="7"/>
+        <v>251</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="15">
         <v>9</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>149</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="D11" s="7"/>
       <c r="E11">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3984,14 +4020,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>252</v>
+        <v>993</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="D12" s="7"/>
+        <v>1007</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>149</v>
+      </c>
       <c r="E12">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -3999,24 +4037,31 @@
         <v>11</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>935</v>
+        <v>994</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>656</v>
-      </c>
-      <c r="D13" s="7"/>
+        <v>995</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E13">
+        <v>12</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="15">
         <v>12</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>657</v>
+        <v>8</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>658</v>
-      </c>
-      <c r="D14" s="7"/>
+        <v>79</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="15">
@@ -4032,7 +4077,82 @@
         <v>149</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>996</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>15</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="23">
+        <v>17</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>998</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>999</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="23">
+        <v>18</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -13028,14 +13148,14 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="33">
+      <c r="A2">
         <v>0</v>
       </c>
-      <c r="B2" s="34" t="s">
-        <v>940</v>
-      </c>
-      <c r="C2" s="33" t="s">
-        <v>974</v>
+      <c r="B2" s="12" t="s">
+        <v>935</v>
+      </c>
+      <c r="C2" t="s">
+        <v>969</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>149</v>
@@ -13048,11 +13168,11 @@
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="35" t="s">
-        <v>958</v>
+      <c r="B3" s="33" t="s">
+        <v>953</v>
       </c>
       <c r="C3" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="E3">
         <v>15</v>
@@ -13062,11 +13182,11 @@
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="35" t="s">
-        <v>959</v>
+      <c r="B4" s="33" t="s">
+        <v>954</v>
       </c>
       <c r="C4" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="E4">
         <v>16</v>
@@ -13076,11 +13196,11 @@
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" s="35" t="s">
-        <v>979</v>
+      <c r="B5" s="33" t="s">
+        <v>974</v>
       </c>
       <c r="C5" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="E5">
         <v>17</v>
@@ -13090,11 +13210,11 @@
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>960</v>
+      <c r="B6" s="33" t="s">
+        <v>955</v>
       </c>
       <c r="C6" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="E6">
         <v>18</v>
@@ -13104,11 +13224,11 @@
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" s="34" t="s">
-        <v>941</v>
-      </c>
-      <c r="C7" s="33" t="s">
-        <v>942</v>
+      <c r="B7" s="12" t="s">
+        <v>936</v>
+      </c>
+      <c r="C7" t="s">
+        <v>937</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7">
@@ -13119,11 +13239,11 @@
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="B8" s="12" t="s">
         <v>860</v>
       </c>
-      <c r="C8" s="33" t="s">
-        <v>962</v>
+      <c r="C8" t="s">
+        <v>957</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>149</v>
@@ -13133,22 +13253,22 @@
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>961</v>
+      <c r="B9" s="33" t="s">
+        <v>956</v>
       </c>
       <c r="C9" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" s="34" t="s">
-        <v>943</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>975</v>
+      <c r="B10" s="12" t="s">
+        <v>938</v>
+      </c>
+      <c r="C10" t="s">
+        <v>970</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>149</v>
@@ -13161,11 +13281,11 @@
       <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>964</v>
+      <c r="B11" s="33" t="s">
+        <v>959</v>
       </c>
       <c r="C11" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -13175,11 +13295,11 @@
       <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" s="35" t="s">
-        <v>965</v>
+      <c r="B12" s="33" t="s">
+        <v>960</v>
       </c>
       <c r="C12" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="E12">
         <v>6</v>
@@ -13189,11 +13309,11 @@
       <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" s="35" t="s">
-        <v>980</v>
+      <c r="B13" s="33" t="s">
+        <v>975</v>
       </c>
       <c r="C13" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="E13">
         <v>7</v>
@@ -13203,11 +13323,11 @@
       <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" s="35" t="s">
-        <v>966</v>
+      <c r="B14" s="33" t="s">
+        <v>961</v>
       </c>
       <c r="C14" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="E14">
         <v>8</v>
@@ -13217,11 +13337,11 @@
       <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" s="34" t="s">
-        <v>944</v>
-      </c>
-      <c r="C15" s="33" t="s">
-        <v>945</v>
+      <c r="B15" s="12" t="s">
+        <v>939</v>
+      </c>
+      <c r="C15" t="s">
+        <v>940</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15">
@@ -13232,11 +13352,11 @@
       <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" s="34" t="s">
-        <v>946</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>947</v>
+      <c r="B16" s="12" t="s">
+        <v>941</v>
+      </c>
+      <c r="C16" t="s">
+        <v>942</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16">
@@ -13247,11 +13367,11 @@
       <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" s="34" t="s">
-        <v>948</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>949</v>
+      <c r="B17" s="12" t="s">
+        <v>943</v>
+      </c>
+      <c r="C17" t="s">
+        <v>944</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17">
@@ -13262,11 +13382,11 @@
       <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="12" t="s">
         <v>290</v>
       </c>
-      <c r="C18" s="33" t="s">
-        <v>967</v>
+      <c r="C18" t="s">
+        <v>962</v>
       </c>
       <c r="D18" s="7"/>
     </row>
@@ -13274,55 +13394,55 @@
       <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="35" t="s">
-        <v>968</v>
+      <c r="B19" s="33" t="s">
+        <v>963</v>
       </c>
       <c r="C19" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" s="35" t="s">
-        <v>969</v>
+      <c r="B20" s="33" t="s">
+        <v>964</v>
       </c>
       <c r="C20" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" s="35" t="s">
-        <v>981</v>
+      <c r="B21" s="33" t="s">
+        <v>976</v>
       </c>
       <c r="C21" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" s="35" t="s">
-        <v>970</v>
+      <c r="B22" s="33" t="s">
+        <v>965</v>
       </c>
       <c r="C22" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B23" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="C23" s="33" t="s">
-        <v>950</v>
+      <c r="C23" t="s">
+        <v>945</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23">
@@ -13333,11 +13453,11 @@
       <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" s="34" t="s">
-        <v>951</v>
-      </c>
-      <c r="C24" s="33" t="s">
-        <v>952</v>
+      <c r="B24" s="12" t="s">
+        <v>946</v>
+      </c>
+      <c r="C24" t="s">
+        <v>947</v>
       </c>
       <c r="D24" s="7" t="s">
         <v>149</v>
@@ -13347,10 +13467,10 @@
       <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" s="34" t="s">
-        <v>953</v>
-      </c>
-      <c r="C25" s="33" t="s">
+      <c r="B25" s="12" t="s">
+        <v>948</v>
+      </c>
+      <c r="C25" t="s">
         <v>287</v>
       </c>
       <c r="D25" s="7"/>
@@ -13362,10 +13482,10 @@
       <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" t="s">
         <v>328</v>
       </c>
       <c r="D26" s="7" t="s">
@@ -13379,10 +13499,10 @@
       <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" t="s">
         <v>330</v>
       </c>
       <c r="D27" s="7"/>
@@ -13394,11 +13514,11 @@
       <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" s="34" t="s">
-        <v>954</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>955</v>
+      <c r="B28" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="C28" t="s">
+        <v>950</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28">
@@ -13409,11 +13529,11 @@
       <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C29" s="33" t="s">
-        <v>956</v>
+      <c r="C29" t="s">
+        <v>951</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29">
@@ -13424,11 +13544,11 @@
       <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" s="34" t="s">
-        <v>957</v>
-      </c>
-      <c r="C30" s="33" t="s">
-        <v>976</v>
+      <c r="B30" s="12" t="s">
+        <v>952</v>
+      </c>
+      <c r="C30" t="s">
+        <v>971</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>149</v>
@@ -13441,11 +13561,11 @@
       <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" s="35" t="s">
-        <v>971</v>
+      <c r="B31" s="33" t="s">
+        <v>966</v>
       </c>
       <c r="C31" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="E31">
         <v>10</v>
@@ -13455,11 +13575,11 @@
       <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" s="35" t="s">
-        <v>972</v>
+      <c r="B32" s="33" t="s">
+        <v>967</v>
       </c>
       <c r="C32" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="E32">
         <v>11</v>
@@ -13469,11 +13589,11 @@
       <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" s="35" t="s">
-        <v>982</v>
+      <c r="B33" s="33" t="s">
+        <v>977</v>
       </c>
       <c r="C33" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E33">
         <v>12</v>
@@ -13483,11 +13603,11 @@
       <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" s="35" t="s">
-        <v>973</v>
+      <c r="B34" s="33" t="s">
+        <v>968</v>
       </c>
       <c r="C34" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="E34">
         <v>13</v>
@@ -18148,10 +18268,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="C14" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="E14">
         <v>11</v>
@@ -18162,10 +18282,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="C15" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="E15">
         <v>12</v>

--- a/Customized Program Main Dataframe Structure.xlsx
+++ b/Customized Program Main Dataframe Structure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0FC01E-97E2-4DA2-8AAB-BE87616C63C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881122C6-566A-4CA0-B8DF-3D3D23E8EABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{B2D932DB-2183-440F-AF66-43F3E8354BB0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{B2D932DB-2183-440F-AF66-43F3E8354BB0}"/>
   </bookViews>
   <sheets>
     <sheet name="05 - mastery_header" sheetId="3" r:id="rId1"/>
@@ -28,9 +28,9 @@
     <sheet name="12 - player_loot_header" sheetId="11" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'05 - LoLGame_info_header'!$A$1:$E$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'05 - LoLGame_info_header'!$A$1:$E$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'05 - TFTHistory_header'!$A$1:$E$160</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'11 - LoLGame_info_header'!$A$1:$E$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'11 - LoLGame_info_header'!$A$1:$E$153</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'11 - TFTHistory_header'!$A$1:$E$160</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2361" uniqueCount="1008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2377" uniqueCount="1016">
   <si>
     <t>gameCreationDate</t>
   </si>
@@ -3259,6 +3259,38 @@
   </si>
   <si>
     <t>下一级成就所需英雄成就标记个数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerAugment5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerAugment5_rarity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerAugment6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>playerAugment6_rarity</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文5等级</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>强化符文6等级</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5093,7 +5125,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86E653D2-5962-4B6A-AE49-EF482E17CB95}">
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
@@ -5500,7 +5532,7 @@
       </c>
       <c r="D26" s="7"/>
       <c r="E26">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5543,7 +5575,7 @@
         <v>149</v>
       </c>
       <c r="E29">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5577,7 +5609,7 @@
         <v>149</v>
       </c>
       <c r="E31">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5594,7 +5626,7 @@
         <v>149</v>
       </c>
       <c r="E32">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5611,7 +5643,7 @@
         <v>149</v>
       </c>
       <c r="E33">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5628,7 +5660,7 @@
         <v>149</v>
       </c>
       <c r="E34">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5659,7 +5691,7 @@
         <v>149</v>
       </c>
       <c r="E36">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5676,7 +5708,7 @@
         <v>149</v>
       </c>
       <c r="E37">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5693,7 +5725,7 @@
         <v>149</v>
       </c>
       <c r="E38">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5710,7 +5742,7 @@
         <v>149</v>
       </c>
       <c r="E39">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5727,7 +5759,7 @@
         <v>149</v>
       </c>
       <c r="E40">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5744,7 +5776,7 @@
         <v>149</v>
       </c>
       <c r="E41">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5761,7 +5793,7 @@
         <v>149</v>
       </c>
       <c r="E42">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5778,7 +5810,7 @@
         <v>149</v>
       </c>
       <c r="E43">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5795,7 +5827,7 @@
         <v>149</v>
       </c>
       <c r="E44">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5812,7 +5844,7 @@
         <v>149</v>
       </c>
       <c r="E45">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5829,7 +5861,7 @@
         <v>149</v>
       </c>
       <c r="E46">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5846,7 +5878,7 @@
         <v>149</v>
       </c>
       <c r="E47">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5863,7 +5895,7 @@
         <v>149</v>
       </c>
       <c r="E48">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -5985,7 +6017,7 @@
         <v>149</v>
       </c>
       <c r="E56">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6016,7 +6048,7 @@
         <v>149</v>
       </c>
       <c r="E58">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6033,7 +6065,7 @@
         <v>149</v>
       </c>
       <c r="E59">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6050,7 +6082,7 @@
         <v>149</v>
       </c>
       <c r="E60">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6067,7 +6099,7 @@
         <v>149</v>
       </c>
       <c r="E61">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6084,7 +6116,7 @@
         <v>149</v>
       </c>
       <c r="E62">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6101,7 +6133,7 @@
         <v>149</v>
       </c>
       <c r="E63">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6118,7 +6150,7 @@
         <v>149</v>
       </c>
       <c r="E64">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6135,7 +6167,7 @@
         <v>149</v>
       </c>
       <c r="E65">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6152,7 +6184,7 @@
         <v>149</v>
       </c>
       <c r="E66">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6169,7 +6201,7 @@
         <v>149</v>
       </c>
       <c r="E67">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6200,7 +6232,7 @@
         <v>149</v>
       </c>
       <c r="E69">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6215,7 +6247,7 @@
       </c>
       <c r="D70" s="7"/>
       <c r="E70">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6230,7 +6262,7 @@
       </c>
       <c r="D71" s="7"/>
       <c r="E71">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6287,7 +6319,7 @@
       </c>
       <c r="D75" s="7"/>
       <c r="E75">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6302,7 +6334,7 @@
       </c>
       <c r="D76" s="7"/>
       <c r="E76">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6359,7 +6391,7 @@
       </c>
       <c r="D80" s="7"/>
       <c r="E80">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6374,7 +6406,7 @@
       </c>
       <c r="D81" s="7"/>
       <c r="E81">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6431,7 +6463,7 @@
       </c>
       <c r="D85" s="7"/>
       <c r="E85">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6446,7 +6478,7 @@
       </c>
       <c r="D86" s="7"/>
       <c r="E86">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6503,7 +6535,7 @@
       </c>
       <c r="D90" s="7"/>
       <c r="E90">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6518,7 +6550,7 @@
       </c>
       <c r="D91" s="7"/>
       <c r="E91">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6575,7 +6607,7 @@
       </c>
       <c r="D95" s="7"/>
       <c r="E95">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6590,7 +6622,7 @@
       </c>
       <c r="D96" s="7"/>
       <c r="E96">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6647,7 +6679,7 @@
       </c>
       <c r="D100" s="7"/>
       <c r="E100">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6662,7 +6694,7 @@
       </c>
       <c r="D101" s="7"/>
       <c r="E101">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6679,7 +6711,7 @@
         <v>149</v>
       </c>
       <c r="E102">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6696,7 +6728,7 @@
         <v>149</v>
       </c>
       <c r="E103">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6713,7 +6745,7 @@
         <v>149</v>
       </c>
       <c r="E104">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6841,27 +6873,29 @@
         <v>111</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>734</v>
+        <v>1008</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>149</v>
+        <v>1012</v>
+      </c>
+      <c r="D113" s="7"/>
+      <c r="E113">
+        <v>35</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A114" s="3">
         <v>112</v>
       </c>
-      <c r="B114" s="4" t="s">
-        <v>735</v>
+      <c r="B114" s="17" t="s">
+        <v>1009</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>149</v>
+        <v>1013</v>
+      </c>
+      <c r="D114" s="7"/>
+      <c r="E114">
+        <v>36</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6869,27 +6903,29 @@
         <v>113</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>736</v>
+        <v>1010</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>149</v>
+        <v>1014</v>
+      </c>
+      <c r="D115" s="7"/>
+      <c r="E115">
+        <v>37</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="3">
         <v>114</v>
       </c>
-      <c r="B116" s="4" t="s">
-        <v>737</v>
+      <c r="B116" s="17" t="s">
+        <v>1011</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>149</v>
+        <v>1015</v>
+      </c>
+      <c r="D116" s="7"/>
+      <c r="E116">
+        <v>38</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -6897,10 +6933,10 @@
         <v>115</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>149</v>
@@ -6911,10 +6947,10 @@
         <v>116</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>149</v>
@@ -6925,10 +6961,10 @@
         <v>117</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="D119" s="7" t="s">
         <v>149</v>
@@ -6939,10 +6975,10 @@
         <v>118</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>149</v>
@@ -6953,10 +6989,10 @@
         <v>119</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>149</v>
@@ -6967,10 +7003,10 @@
         <v>120</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>149</v>
@@ -6981,28 +7017,27 @@
         <v>121</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>288</v>
+        <v>740</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D123" s="7"/>
+        <v>750</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="124" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A124" s="3">
         <v>122</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>50</v>
+        <v>741</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>123</v>
+        <v>751</v>
       </c>
       <c r="D124" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="E124">
-        <v>50</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7010,16 +7045,13 @@
         <v>123</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>316</v>
+        <v>742</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>124</v>
+        <v>752</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="E125">
-        <v>76</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7027,10 +7059,10 @@
         <v>124</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>51</v>
+        <v>743</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>317</v>
+        <v>753</v>
       </c>
       <c r="D126" s="7" t="s">
         <v>149</v>
@@ -7041,33 +7073,28 @@
         <v>125</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E127">
-        <v>103</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="D127" s="7"/>
     </row>
     <row r="128" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A128" s="3">
         <v>126</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E128">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7075,16 +7102,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>53</v>
+        <v>316</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E129">
-        <v>59</v>
+        <v>80</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7092,16 +7119,13 @@
         <v>128</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>127</v>
+        <v>317</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="E130">
-        <v>55</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7109,16 +7133,16 @@
         <v>129</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>55</v>
+        <v>318</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>128</v>
+        <v>319</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E131">
-        <v>68</v>
+        <v>107</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7126,16 +7150,16 @@
         <v>130</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E132">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7143,16 +7167,16 @@
         <v>131</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D133" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E133">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7160,16 +7184,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E134">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7177,16 +7201,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E135">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7194,16 +7218,16 @@
         <v>134</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D136" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E136">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7211,16 +7235,16 @@
         <v>135</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E137">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7228,16 +7252,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D138" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E138">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7245,16 +7269,16 @@
         <v>137</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E139">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7262,10 +7286,10 @@
         <v>138</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D140" s="7" t="s">
         <v>149</v>
@@ -7279,10 +7303,10 @@
         <v>139</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>320</v>
+        <v>61</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>321</v>
+        <v>134</v>
       </c>
       <c r="D141" s="7" t="s">
         <v>149</v>
@@ -7296,16 +7320,16 @@
         <v>140</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D142" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E142">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7313,16 +7337,16 @@
         <v>141</v>
       </c>
       <c r="B143" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E143">
         <v>66</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D143" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E143">
-        <v>52</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7330,16 +7354,16 @@
         <v>142</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D144" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E144">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7347,16 +7371,16 @@
         <v>143</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>141</v>
+        <v>321</v>
       </c>
       <c r="D145" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E145">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7364,16 +7388,16 @@
         <v>144</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D146" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E146">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -7381,49 +7405,120 @@
         <v>145</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D147" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E147">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A148" s="3">
         <v>146</v>
       </c>
-      <c r="B148" s="17" t="s">
+      <c r="B148" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E148">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A149" s="3">
+        <v>147</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E149">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A150" s="3">
+        <v>148</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E150">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A151" s="3">
+        <v>149</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D151" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E151">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A152" s="3">
+        <v>150</v>
+      </c>
+      <c r="B152" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="C152" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D148" s="7"/>
-      <c r="E148">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A149" s="8">
-        <v>147</v>
-      </c>
-      <c r="B149" s="9" t="s">
+      <c r="D152" s="7"/>
+      <c r="E152">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A153" s="8">
+        <v>151</v>
+      </c>
+      <c r="B153" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="C149" s="8" t="s">
+      <c r="C153" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D149" s="7"/>
-      <c r="E149">
+      <c r="D153" s="7"/>
+      <c r="E153">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E153">
+    <sortCondition ref="A1:A153"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9709,6 +9804,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E160">
+    <sortCondition ref="A1:A160"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10565,7 +10663,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A51E86A-E436-491E-8E79-A2D2CA117759}">
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="35" bestFit="1" customWidth="1"/>
@@ -10881,7 +10979,7 @@
         <v>149</v>
       </c>
       <c r="E20">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -10898,7 +10996,7 @@
         <v>149</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -10932,7 +11030,7 @@
         <v>149</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -10949,7 +11047,7 @@
         <v>149</v>
       </c>
       <c r="E24">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -10966,7 +11064,7 @@
         <v>149</v>
       </c>
       <c r="E25">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -10983,7 +11081,7 @@
         <v>149</v>
       </c>
       <c r="E26">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11000,7 +11098,7 @@
         <v>149</v>
       </c>
       <c r="E27">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11017,7 +11115,7 @@
         <v>149</v>
       </c>
       <c r="E28">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11034,7 +11132,7 @@
         <v>149</v>
       </c>
       <c r="E29">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11051,7 +11149,7 @@
         <v>149</v>
       </c>
       <c r="E30">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11068,7 +11166,7 @@
         <v>149</v>
       </c>
       <c r="E31">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11085,7 +11183,7 @@
         <v>149</v>
       </c>
       <c r="E32">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11102,7 +11200,7 @@
         <v>149</v>
       </c>
       <c r="E33">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11119,7 +11217,7 @@
         <v>149</v>
       </c>
       <c r="E34">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11136,7 +11234,7 @@
         <v>149</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11153,7 +11251,7 @@
         <v>149</v>
       </c>
       <c r="E36">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11170,7 +11268,7 @@
         <v>149</v>
       </c>
       <c r="E37">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11187,7 +11285,7 @@
         <v>149</v>
       </c>
       <c r="E38">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11204,7 +11302,7 @@
         <v>149</v>
       </c>
       <c r="E39">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11221,7 +11319,7 @@
         <v>149</v>
       </c>
       <c r="E40">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11343,7 +11441,7 @@
         <v>149</v>
       </c>
       <c r="E48">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11360,7 +11458,7 @@
         <v>149</v>
       </c>
       <c r="E49">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11377,7 +11475,7 @@
         <v>149</v>
       </c>
       <c r="E50">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11394,7 +11492,7 @@
         <v>149</v>
       </c>
       <c r="E51">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11411,7 +11509,7 @@
         <v>149</v>
       </c>
       <c r="E52">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11428,7 +11526,7 @@
         <v>149</v>
       </c>
       <c r="E53">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11445,7 +11543,7 @@
         <v>149</v>
       </c>
       <c r="E54">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11462,7 +11560,7 @@
         <v>149</v>
       </c>
       <c r="E55">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11479,7 +11577,7 @@
         <v>149</v>
       </c>
       <c r="E56">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11496,7 +11594,7 @@
         <v>149</v>
       </c>
       <c r="E57">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11513,7 +11611,7 @@
         <v>149</v>
       </c>
       <c r="E58">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11530,7 +11628,7 @@
         <v>149</v>
       </c>
       <c r="E59">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11561,7 +11659,7 @@
         <v>149</v>
       </c>
       <c r="E61">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11576,7 +11674,7 @@
       </c>
       <c r="D62" s="7"/>
       <c r="E62">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11591,7 +11689,7 @@
       </c>
       <c r="D63" s="7"/>
       <c r="E63">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11648,7 +11746,7 @@
       </c>
       <c r="D67" s="7"/>
       <c r="E67">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11663,7 +11761,7 @@
       </c>
       <c r="D68" s="7"/>
       <c r="E68">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11720,7 +11818,7 @@
       </c>
       <c r="D72" s="7"/>
       <c r="E72">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11735,7 +11833,7 @@
       </c>
       <c r="D73" s="7"/>
       <c r="E73">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11792,7 +11890,7 @@
       </c>
       <c r="D77" s="7"/>
       <c r="E77">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11807,7 +11905,7 @@
       </c>
       <c r="D78" s="7"/>
       <c r="E78">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11864,7 +11962,7 @@
       </c>
       <c r="D82" s="7"/>
       <c r="E82">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11879,7 +11977,7 @@
       </c>
       <c r="D83" s="7"/>
       <c r="E83">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11936,7 +12034,7 @@
       </c>
       <c r="D87" s="7"/>
       <c r="E87">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11951,7 +12049,7 @@
       </c>
       <c r="D88" s="7"/>
       <c r="E88">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12008,7 +12106,7 @@
       </c>
       <c r="D92" s="7"/>
       <c r="E92">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12023,7 +12121,7 @@
       </c>
       <c r="D93" s="7"/>
       <c r="E93">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12040,7 +12138,7 @@
         <v>149</v>
       </c>
       <c r="E94">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12057,7 +12155,7 @@
         <v>149</v>
       </c>
       <c r="E95">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12074,7 +12172,7 @@
         <v>149</v>
       </c>
       <c r="E96">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12202,27 +12300,29 @@
         <v>103</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>734</v>
+        <v>1008</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>149</v>
+        <v>1012</v>
+      </c>
+      <c r="D105" s="7"/>
+      <c r="E105">
+        <v>32</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="3">
         <v>104</v>
       </c>
-      <c r="B106" s="4" t="s">
-        <v>735</v>
+      <c r="B106" s="17" t="s">
+        <v>1009</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>149</v>
+        <v>1013</v>
+      </c>
+      <c r="D106" s="7"/>
+      <c r="E106">
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12230,27 +12330,29 @@
         <v>105</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>736</v>
+        <v>1010</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="D107" s="7" t="s">
-        <v>149</v>
+        <v>1014</v>
+      </c>
+      <c r="D107" s="7"/>
+      <c r="E107">
+        <v>34</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A108" s="3">
         <v>106</v>
       </c>
-      <c r="B108" s="4" t="s">
-        <v>737</v>
+      <c r="B108" s="17" t="s">
+        <v>1011</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>149</v>
+        <v>1015</v>
+      </c>
+      <c r="D108" s="7"/>
+      <c r="E108">
+        <v>35</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12258,10 +12360,10 @@
         <v>107</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="D109" s="7" t="s">
         <v>149</v>
@@ -12272,10 +12374,10 @@
         <v>108</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="D110" s="7" t="s">
         <v>149</v>
@@ -12286,10 +12388,10 @@
         <v>109</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="D111" s="7" t="s">
         <v>149</v>
@@ -12300,10 +12402,10 @@
         <v>110</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="D112" s="7" t="s">
         <v>149</v>
@@ -12314,10 +12416,10 @@
         <v>111</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="D113" s="7" t="s">
         <v>149</v>
@@ -12328,10 +12430,10 @@
         <v>112</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="D114" s="7" t="s">
         <v>149</v>
@@ -12342,14 +12444,13 @@
         <v>113</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>288</v>
+        <v>740</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="D115" s="7"/>
-      <c r="E115">
-        <v>1</v>
+        <v>750</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12357,16 +12458,13 @@
         <v>114</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>50</v>
+        <v>741</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>123</v>
+        <v>751</v>
       </c>
       <c r="D116" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="E116">
-        <v>49</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12374,16 +12472,13 @@
         <v>115</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>316</v>
+        <v>742</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>124</v>
+        <v>752</v>
       </c>
       <c r="D117" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="E117">
-        <v>75</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12391,16 +12486,13 @@
         <v>116</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>51</v>
+        <v>743</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>317</v>
+        <v>753</v>
       </c>
       <c r="D118" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="E118">
-        <v>106</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12408,16 +12500,14 @@
         <v>117</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>149</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="D119" s="7"/>
       <c r="E119">
-        <v>102</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12425,16 +12515,16 @@
         <v>118</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E120">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12442,16 +12532,16 @@
         <v>119</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>53</v>
+        <v>316</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D121" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E121">
-        <v>58</v>
+        <v>79</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12459,16 +12549,16 @@
         <v>120</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>127</v>
+        <v>317</v>
       </c>
       <c r="D122" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E122">
-        <v>54</v>
+        <v>110</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12476,16 +12566,16 @@
         <v>121</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>55</v>
+        <v>318</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>128</v>
+        <v>319</v>
       </c>
       <c r="D123" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E123">
-        <v>67</v>
+        <v>106</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12493,16 +12583,16 @@
         <v>122</v>
       </c>
       <c r="B124" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E124">
         <v>56</v>
-      </c>
-      <c r="C124" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E124">
-        <v>65</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12510,16 +12600,16 @@
         <v>123</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="D125" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E125">
-        <v>79</v>
+        <v>62</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12527,16 +12617,16 @@
         <v>124</v>
       </c>
       <c r="B126" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E126">
         <v>58</v>
-      </c>
-      <c r="C126" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E126">
-        <v>36</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12544,16 +12634,16 @@
         <v>125</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D127" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E127">
-        <v>37</v>
+        <v>71</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12561,16 +12651,16 @@
         <v>126</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D128" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E128">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12578,16 +12668,16 @@
         <v>127</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D129" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E129">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12595,16 +12685,16 @@
         <v>128</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D130" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E130">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12612,16 +12702,16 @@
         <v>129</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="D131" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E131">
-        <v>61</v>
+        <v>41</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12629,10 +12719,10 @@
         <v>130</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D132" s="7" t="s">
         <v>149</v>
@@ -12646,10 +12736,10 @@
         <v>131</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>320</v>
+        <v>61</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>321</v>
+        <v>134</v>
       </c>
       <c r="D133" s="7" t="s">
         <v>149</v>
@@ -12663,16 +12753,16 @@
         <v>132</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D134" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E134">
-        <v>83</v>
+        <v>52</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12680,16 +12770,16 @@
         <v>133</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D135" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E135">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12697,16 +12787,16 @@
         <v>134</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D136" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E136">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12714,16 +12804,16 @@
         <v>135</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>141</v>
+        <v>321</v>
       </c>
       <c r="D137" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E137">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12731,16 +12821,16 @@
         <v>136</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D138" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E138">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12748,64 +12838,135 @@
         <v>137</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D139" s="7" t="s">
         <v>149</v>
       </c>
       <c r="E139">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15" x14ac:dyDescent="0.2">
       <c r="A140" s="3">
         <v>138</v>
       </c>
-      <c r="B140" s="17" t="s">
+      <c r="B140" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D140" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E140">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A141" s="3">
+        <v>139</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D141" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E141">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A142" s="3">
+        <v>140</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E142">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A143" s="3">
+        <v>141</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E143">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A144" s="3">
+        <v>142</v>
+      </c>
+      <c r="B144" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="C140" s="3" t="s">
+      <c r="C144" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D140" s="7"/>
-      <c r="E140">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A141" s="23">
-        <v>139</v>
-      </c>
-      <c r="B141" s="24" t="s">
+      <c r="D144" s="7"/>
+      <c r="E144">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A145" s="23">
+        <v>143</v>
+      </c>
+      <c r="B145" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="C141" s="23" t="s">
+      <c r="C145" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D141" s="7"/>
-      <c r="E141">
+      <c r="D145" s="7"/>
+      <c r="E145">
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="A142" s="23">
-        <v>140</v>
-      </c>
-      <c r="B142" s="24" t="s">
+    <row r="146" spans="1:5" ht="15" x14ac:dyDescent="0.2">
+      <c r="A146" s="23">
+        <v>144</v>
+      </c>
+      <c r="B146" s="24" t="s">
         <v>297</v>
       </c>
-      <c r="C142" s="23" t="s">
+      <c r="C146" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="D142" s="7"/>
-      <c r="E142">
+      <c r="D146" s="7"/>
+      <c r="E146">
         <v>13</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E146">
+    <sortCondition ref="A1:A146"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/Customized Program Main Dataframe Structure.xlsx
+++ b/Customized Program Main Dataframe Structure.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\19250\Documents\GitHub\LoL-DIY-Programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D2F465-ECA9-4961-B4E5-E0C7D1C9AEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB8CCA1D-33E0-41B1-9CF5-0DDEE2A807F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" firstSheet="50" activeTab="53" xr2:uid="{B2D932DB-2183-440F-AF66-43F3E8354BB0}"/>
+    <workbookView xWindow="2730" yWindow="1755" windowWidth="33540" windowHeight="17550" firstSheet="9" activeTab="9" xr2:uid="{B2D932DB-2183-440F-AF66-43F3E8354BB0}"/>
   </bookViews>
   <sheets>
     <sheet name="04 - LoLChampions_header (LCU)" sheetId="17" r:id="rId1"/>
@@ -11717,7 +11717,7 @@
         <v>138</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -11763,7 +11763,7 @@
         <v>138</v>
       </c>
       <c r="E8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -11793,6 +11793,9 @@
       <c r="D10" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="E10">
+        <v>7</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="13">
@@ -11892,7 +11895,7 @@
         <v>1125</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11948,7 +11951,7 @@
         <v>1239</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11962,7 +11965,7 @@
         <v>1240</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -11987,7 +11990,7 @@
         <v>1149</v>
       </c>
       <c r="E24">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12001,7 +12004,7 @@
         <v>1150</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12040,7 +12043,7 @@
         <v>138</v>
       </c>
       <c r="E28">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12057,7 +12060,7 @@
         <v>138</v>
       </c>
       <c r="E29">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12074,7 +12077,7 @@
         <v>138</v>
       </c>
       <c r="E30">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12091,7 +12094,7 @@
         <v>138</v>
       </c>
       <c r="E31">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12108,7 +12111,7 @@
         <v>138</v>
       </c>
       <c r="E32">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12125,7 +12128,7 @@
         <v>138</v>
       </c>
       <c r="E33">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12142,7 +12145,7 @@
         <v>138</v>
       </c>
       <c r="E34">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12159,7 +12162,7 @@
         <v>138</v>
       </c>
       <c r="E35">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12176,7 +12179,7 @@
         <v>138</v>
       </c>
       <c r="E36">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12193,7 +12196,7 @@
         <v>138</v>
       </c>
       <c r="E37">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12210,7 +12213,7 @@
         <v>138</v>
       </c>
       <c r="E38">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12227,7 +12230,7 @@
         <v>138</v>
       </c>
       <c r="E39">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12244,7 +12247,7 @@
         <v>138</v>
       </c>
       <c r="E40">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12261,7 +12264,7 @@
         <v>138</v>
       </c>
       <c r="E41">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12278,7 +12281,7 @@
         <v>138</v>
       </c>
       <c r="E42">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12295,7 +12298,7 @@
         <v>138</v>
       </c>
       <c r="E43">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12312,7 +12315,7 @@
         <v>138</v>
       </c>
       <c r="E44">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12329,7 +12332,7 @@
         <v>138</v>
       </c>
       <c r="E45">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12346,7 +12349,7 @@
         <v>138</v>
       </c>
       <c r="E46">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12363,7 +12366,7 @@
         <v>138</v>
       </c>
       <c r="E47">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12380,7 +12383,7 @@
         <v>138</v>
       </c>
       <c r="E48">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12495,7 +12498,7 @@
         <v>138</v>
       </c>
       <c r="E56">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12512,7 +12515,7 @@
         <v>138</v>
       </c>
       <c r="E57">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12529,7 +12532,7 @@
         <v>138</v>
       </c>
       <c r="E58">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12546,7 +12549,7 @@
         <v>138</v>
       </c>
       <c r="E59">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12563,7 +12566,7 @@
         <v>138</v>
       </c>
       <c r="E60">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12580,7 +12583,7 @@
         <v>138</v>
       </c>
       <c r="E61">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12597,7 +12600,7 @@
         <v>138</v>
       </c>
       <c r="E62">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12614,7 +12617,7 @@
         <v>138</v>
       </c>
       <c r="E63">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12631,7 +12634,7 @@
         <v>138</v>
       </c>
       <c r="E64">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12648,7 +12651,7 @@
         <v>138</v>
       </c>
       <c r="E65">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="66" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12665,7 +12668,7 @@
         <v>138</v>
       </c>
       <c r="E66">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12682,7 +12685,7 @@
         <v>138</v>
       </c>
       <c r="E67">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -12713,7 +12716,7 @@
         <v>138</v>
       </c>
       <c r="E69">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13094,7 +13097,7 @@
         <v>138</v>
       </c>
       <c r="E96">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13111,7 +13114,7 @@
         <v>138</v>
       </c>
       <c r="E97">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13128,7 +13131,7 @@
         <v>138</v>
       </c>
       <c r="E98">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13383,7 +13386,7 @@
         <v>138</v>
       </c>
       <c r="E116">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13400,7 +13403,7 @@
         <v>138</v>
       </c>
       <c r="E117">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13417,7 +13420,7 @@
         <v>138</v>
       </c>
       <c r="E118">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="119" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13434,7 +13437,7 @@
         <v>138</v>
       </c>
       <c r="E119">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13451,7 +13454,7 @@
         <v>138</v>
       </c>
       <c r="E120">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="121" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13468,7 +13471,7 @@
         <v>138</v>
       </c>
       <c r="E121">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="122" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13485,7 +13488,7 @@
         <v>138</v>
       </c>
       <c r="E122">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13502,7 +13505,7 @@
         <v>138</v>
       </c>
       <c r="E123">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13519,7 +13522,7 @@
         <v>138</v>
       </c>
       <c r="E124">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="125" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13536,7 +13539,7 @@
         <v>138</v>
       </c>
       <c r="E125">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13553,7 +13556,7 @@
         <v>138</v>
       </c>
       <c r="E126">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="127" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13570,7 +13573,7 @@
         <v>138</v>
       </c>
       <c r="E127">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="128" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13587,7 +13590,7 @@
         <v>138</v>
       </c>
       <c r="E128">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13604,7 +13607,7 @@
         <v>138</v>
       </c>
       <c r="E129">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13621,7 +13624,7 @@
         <v>138</v>
       </c>
       <c r="E130">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13638,7 +13641,7 @@
         <v>138</v>
       </c>
       <c r="E131">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13655,7 +13658,7 @@
         <v>138</v>
       </c>
       <c r="E132">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13672,7 +13675,7 @@
         <v>138</v>
       </c>
       <c r="E133">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13689,7 +13692,7 @@
         <v>138</v>
       </c>
       <c r="E134">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13706,7 +13709,7 @@
         <v>138</v>
       </c>
       <c r="E135">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="136" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13723,7 +13726,7 @@
         <v>138</v>
       </c>
       <c r="E136">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13740,7 +13743,7 @@
         <v>138</v>
       </c>
       <c r="E137">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13757,7 +13760,7 @@
         <v>138</v>
       </c>
       <c r="E138">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13774,7 +13777,7 @@
         <v>138</v>
       </c>
       <c r="E139">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="140" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13802,7 +13805,7 @@
         <v>92</v>
       </c>
       <c r="E141">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13816,7 +13819,7 @@
         <v>93</v>
       </c>
       <c r="E142">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13830,7 +13833,7 @@
         <v>94</v>
       </c>
       <c r="E143">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13844,7 +13847,7 @@
         <v>95</v>
       </c>
       <c r="E144">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="145" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13858,7 +13861,7 @@
         <v>96</v>
       </c>
       <c r="E145">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13872,7 +13875,7 @@
         <v>97</v>
       </c>
       <c r="E146">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="147" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13886,7 +13889,7 @@
         <v>98</v>
       </c>
       <c r="E147">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="148" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13977,7 +13980,7 @@
         <v>581</v>
       </c>
       <c r="E155">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="156" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -13991,7 +13994,7 @@
         <v>589</v>
       </c>
       <c r="E156">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="157" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14005,7 +14008,7 @@
         <v>590</v>
       </c>
       <c r="E157">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="158" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14019,7 +14022,7 @@
         <v>591</v>
       </c>
       <c r="E158">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="159" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14033,7 +14036,7 @@
         <v>592</v>
       </c>
       <c r="E159">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="160" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14047,7 +14050,7 @@
         <v>593</v>
       </c>
       <c r="E160">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="161" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14061,7 +14064,7 @@
         <v>1221</v>
       </c>
       <c r="E161">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="162" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14075,7 +14078,7 @@
         <v>1223</v>
       </c>
       <c r="E162">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="163" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14089,7 +14092,7 @@
         <v>1225</v>
       </c>
       <c r="E163">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="164" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14103,7 +14106,7 @@
         <v>1228</v>
       </c>
       <c r="E164">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="165" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14117,7 +14120,7 @@
         <v>1230</v>
       </c>
       <c r="E165">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="166" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14131,7 +14134,7 @@
         <v>1232</v>
       </c>
       <c r="E166">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="167" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14211,7 +14214,7 @@
         <v>1278</v>
       </c>
       <c r="E173">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="174" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14236,7 +14239,7 @@
         <v>1283</v>
       </c>
       <c r="E175">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="176" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14261,7 +14264,7 @@
         <v>1252</v>
       </c>
       <c r="E177">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="178" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14275,7 +14278,7 @@
         <v>1254</v>
       </c>
       <c r="E178">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="179" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14289,7 +14292,7 @@
         <v>1256</v>
       </c>
       <c r="E179">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="180" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14303,7 +14306,7 @@
         <v>1258</v>
       </c>
       <c r="E180">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="181" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14317,7 +14320,7 @@
         <v>1260</v>
       </c>
       <c r="E181">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="182" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14331,7 +14334,7 @@
         <v>1262</v>
       </c>
       <c r="E182">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="183" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14411,7 +14414,7 @@
         <v>624</v>
       </c>
       <c r="E189">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="190" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14425,7 +14428,7 @@
         <v>627</v>
       </c>
       <c r="E190">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="191" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14439,7 +14442,7 @@
         <v>628</v>
       </c>
       <c r="E191">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="192" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14453,7 +14456,7 @@
         <v>629</v>
       </c>
       <c r="E192">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="193" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14467,7 +14470,7 @@
         <v>857</v>
       </c>
       <c r="E193">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="194" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14481,7 +14484,7 @@
         <v>859</v>
       </c>
       <c r="E194">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="195" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14495,7 +14498,7 @@
         <v>298</v>
       </c>
       <c r="E195">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="196" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14520,7 +14523,7 @@
         <v>1247</v>
       </c>
       <c r="E197">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14534,7 +14537,7 @@
         <v>1248</v>
       </c>
       <c r="E198">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="199" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14559,7 +14562,7 @@
         <v>1640</v>
       </c>
       <c r="E200">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="201" spans="1:5" ht="15" x14ac:dyDescent="0.2">
@@ -14573,7 +14576,7 @@
         <v>1642</v>
       </c>
       <c r="E201">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
